--- a/03_Pathway_Enrichment/05_Volcano/c_data/05_volcano.xlsx
+++ b/03_Pathway_Enrichment/05_Volcano/c_data/05_volcano.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="178">
   <si>
     <t>sheet</t>
   </si>
@@ -83,36 +83,39 @@
     <t>REACTOME_AEROBIC_RESPIRATION_AND_RESPIRATORY_ELECTRON_TRANSPORT</t>
   </si>
   <si>
-    <t>GOBP|GOBP_MULTICELLULAR_ORGANISMAL_MOVEMENT</t>
+    <t>GOBP|GOBP_PROTON_TRANSMEMBRANE_TRANSPORT</t>
   </si>
   <si>
     <t>GOBP</t>
   </si>
   <si>
-    <t>GOBP_MULTICELLULAR_ORGANISMAL_MOVEMENT</t>
+    <t>GOBP_PROTON_TRANSMEMBRANE_TRANSPORT</t>
+  </si>
+  <si>
+    <t>KEGG_Legacy|KEGG_PARKINSONS_DISEASE</t>
+  </si>
+  <si>
+    <t>KEGG_Legacy</t>
+  </si>
+  <si>
+    <t>KEGG_PARKINSONS_DISEASE</t>
+  </si>
+  <si>
+    <t>GO_Slim|TRANSMEMBRANE_TRANSPORT</t>
+  </si>
+  <si>
+    <t>GO_Slim</t>
+  </si>
+  <si>
+    <t>transmembrane transport</t>
   </si>
   <si>
     <t>GO_Slim|CYTOSKELETON_ORGANIZATION</t>
   </si>
   <si>
-    <t>GO_Slim</t>
-  </si>
-  <si>
     <t>cytoskeleton organization</t>
   </si>
   <si>
-    <t>GO_Slim|TRANSMEMBRANE_TRANSPORT</t>
-  </si>
-  <si>
-    <t>transmembrane transport</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_PROTON_TRANSMEMBRANE_TRANSPORT</t>
-  </si>
-  <si>
-    <t>GOBP_PROTON_TRANSMEMBRANE_TRANSPORT</t>
-  </si>
-  <si>
     <t>Hallmark|HALLMARK_OXIDATIVE_PHOSPHORYLATION</t>
   </si>
   <si>
@@ -122,13 +125,64 @@
     <t>HALLMARK_OXIDATIVE_PHOSPHORYLATION</t>
   </si>
   <si>
-    <t>KEGG_Legacy|KEGG_PARKINSONS_DISEASE</t>
-  </si>
-  <si>
-    <t>KEGG_Legacy</t>
-  </si>
-  <si>
-    <t>KEGG_PARKINSONS_DISEASE</t>
+    <t>KEGG_Legacy|KEGG_ALZHEIMERS_DISEASE</t>
+  </si>
+  <si>
+    <t>KEGG_ALZHEIMERS_DISEASE</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_NUCLEOTIDE_BIOSYNTHETIC_PROCESS</t>
+  </si>
+  <si>
+    <t>GOBP_NUCLEOTIDE_BIOSYNTHETIC_PROCESS</t>
+  </si>
+  <si>
+    <t>Acute_Interaction</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_GENERATION_OF_PRECURSOR_METABOLITES_AND_ENERGY</t>
+  </si>
+  <si>
+    <t>GOBP_GENERATION_OF_PRECURSOR_METABOLITES_AND_ENERGY</t>
+  </si>
+  <si>
+    <t>KEGG_Legacy|KEGG_HUNTINGTONS_DISEASE</t>
+  </si>
+  <si>
+    <t>KEGG_HUNTINGTONS_DISEASE</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_MITOCHONDRION_ORGANIZATION</t>
+  </si>
+  <si>
+    <t>GOBP_MITOCHONDRION_ORGANIZATION</t>
+  </si>
+  <si>
+    <t>GO_Slim|NUCLEOBASE_CONTAINING_SMALL_MOLECULE_METABOLIC_PROCESS</t>
+  </si>
+  <si>
+    <t>nucleobase-containing small molecule metabolic process</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_MITOCHONDRIAL_RESPIRATORY_CHAIN_COMPLEX_ASSEMBLY</t>
+  </si>
+  <si>
+    <t>GOBP_MITOCHONDRIAL_RESPIRATORY_CHAIN_COMPLEX_ASSEMBLY</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_MITOCHONDRIAL_MEMBRANE_ORGANIZATION</t>
+  </si>
+  <si>
+    <t>GOBP_MITOCHONDRIAL_MEMBRANE_ORGANIZATION</t>
+  </si>
+  <si>
+    <t>Training_HR</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_MITOCHONDRIAL_PROTEIN_DEGRADATION</t>
+  </si>
+  <si>
+    <t>REACTOME_MITOCHONDRIAL_PROTEIN_DEGRADATION</t>
   </si>
   <si>
     <t>Reactome|REACTOME_STRIATED_MUSCLE_CONTRACTION</t>
@@ -137,13 +191,34 @@
     <t>REACTOME_STRIATED_MUSCLE_CONTRACTION</t>
   </si>
   <si>
-    <t>Acute_Interaction</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_ANCHORING_OF_THE_BASAL_BODY_TO_THE_PLASMA_MEMBRANE</t>
-  </si>
-  <si>
-    <t>REACTOME_ANCHORING_OF_THE_BASAL_BODY_TO_THE_PLASMA_MEMBRANE</t>
+    <t>GO_Slim|MUSCLE_SYSTEM_PROCESS</t>
+  </si>
+  <si>
+    <t>muscle system process</t>
+  </si>
+  <si>
+    <t>Training_LR</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_TRICARBOXYLIC_ACID_CYCLE</t>
+  </si>
+  <si>
+    <t>GOBP_TRICARBOXYLIC_ACID_CYCLE</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_SIGNALING_BY_NOTCH</t>
+  </si>
+  <si>
+    <t>REACTOME_SIGNALING_BY_NOTCH</t>
+  </si>
+  <si>
+    <t>Acute_HR</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_CYTOPLASMIC_TRANSLATION</t>
+  </si>
+  <si>
+    <t>GOBP_CYTOPLASMIC_TRANSLATION</t>
   </si>
   <si>
     <t>Reactome|REACTOME_EUKARYOTIC_TRANSLATION_ELONGATION</t>
@@ -152,97 +227,10 @@
     <t>REACTOME_EUKARYOTIC_TRANSLATION_ELONGATION</t>
   </si>
   <si>
-    <t>Hallmark|HALLMARK_HEME_METABOLISM</t>
-  </si>
-  <si>
-    <t>HALLMARK_HEME_METABOLISM</t>
-  </si>
-  <si>
-    <t>GO_Slim|CYTOPLASMIC_TRANSLATION</t>
-  </si>
-  <si>
-    <t>cytoplasmic translation</t>
-  </si>
-  <si>
-    <t>Hallmark|HALLMARK_UNFOLDED_PROTEIN_RESPONSE</t>
-  </si>
-  <si>
-    <t>HALLMARK_UNFOLDED_PROTEIN_RESPONSE</t>
-  </si>
-  <si>
-    <t>Training_HR</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_GENERATION_OF_PRECURSOR_METABOLITES_AND_ENERGY</t>
-  </si>
-  <si>
-    <t>GOBP_GENERATION_OF_PRECURSOR_METABOLITES_AND_ENERGY</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_MITOCHONDRIAL_PROTEIN_DEGRADATION</t>
-  </si>
-  <si>
-    <t>REACTOME_MITOCHONDRIAL_PROTEIN_DEGRADATION</t>
-  </si>
-  <si>
-    <t>KEGG_Legacy|KEGG_HUNTINGTONS_DISEASE</t>
-  </si>
-  <si>
-    <t>KEGG_HUNTINGTONS_DISEASE</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_MITOCHONDRION_ORGANIZATION</t>
-  </si>
-  <si>
-    <t>GOBP_MITOCHONDRION_ORGANIZATION</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_MITOCHONDRIAL_PROTEIN_IMPORT</t>
-  </si>
-  <si>
-    <t>REACTOME_MITOCHONDRIAL_PROTEIN_IMPORT</t>
-  </si>
-  <si>
-    <t>Training_LR</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_NUCLEAR_EVENTS_MEDIATED_BY_NFE2L2</t>
-  </si>
-  <si>
-    <t>REACTOME_NUCLEAR_EVENTS_MEDIATED_BY_NFE2L2</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_CLEC7A_DECTIN_1_SIGNALING</t>
-  </si>
-  <si>
-    <t>REACTOME_CLEC7A_DECTIN_1_SIGNALING</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_SIGNALING_BY_NOTCH</t>
-  </si>
-  <si>
-    <t>REACTOME_SIGNALING_BY_NOTCH</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_NEDDYLATION</t>
-  </si>
-  <si>
-    <t>REACTOME_NEDDYLATION</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_TRICARBOXYLIC_ACID_CYCLE</t>
-  </si>
-  <si>
-    <t>GOBP_TRICARBOXYLIC_ACID_CYCLE</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_ANTIGEN_PROCESSING_UBIQUITINATION_PROTEASOME_DEGRADATION</t>
-  </si>
-  <si>
-    <t>REACTOME_ANTIGEN_PROCESSING_UBIQUITINATION_PROTEASOME_DEGRADATION</t>
-  </si>
-  <si>
-    <t>Acute_HR</t>
+    <t>Reactome|REACTOME_NONSENSE_MEDIATED_DECAY_NMD</t>
+  </si>
+  <si>
+    <t>REACTOME_NONSENSE_MEDIATED_DECAY_NMD</t>
   </si>
   <si>
     <t>Reactome|REACTOME_DENGUE_VIRUS_INFECTION</t>
@@ -251,55 +239,37 @@
     <t>REACTOME_DENGUE_VIRUS_INFECTION</t>
   </si>
   <si>
-    <t>GOBP|GOBP_CYTOPLASMIC_TRANSLATION</t>
-  </si>
-  <si>
-    <t>GOBP_CYTOPLASMIC_TRANSLATION</t>
-  </si>
-  <si>
-    <t>GO_Slim|MRNA_METABOLIC_PROCESS</t>
-  </si>
-  <si>
-    <t>mRNA metabolic process</t>
+    <t>GOBP|GOBP_NEGATIVE_REGULATION_OF_SYNCYTIUM_FORMATION_BY_PLASMA_MEMBRANE_FUSION</t>
+  </si>
+  <si>
+    <t>GOBP_NEGATIVE_REGULATION_OF_SYNCYTIUM_FORMATION_BY_PLASMA_MEMBRANE_FUSION</t>
   </si>
   <si>
     <t>Acute_LR</t>
   </si>
   <si>
-    <t>GOBP|GOBP_RNA_SPLICING_VIA_TRANSESTERIFICATION_REACTIONS</t>
-  </si>
-  <si>
-    <t>GOBP_RNA_SPLICING_VIA_TRANSESTERIFICATION_REACTIONS</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_MRNA_3_END_PROCESSING</t>
-  </si>
-  <si>
-    <t>REACTOME_MRNA_3_END_PROCESSING</t>
-  </si>
-  <si>
-    <t>Hallmark|HALLMARK_MYC_TARGETS_V1</t>
-  </si>
-  <si>
-    <t>HALLMARK_MYC_TARGETS_V1</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_ORGANELLE_BIOGENESIS_AND_MAINTENANCE</t>
-  </si>
-  <si>
-    <t>REACTOME_ORGANELLE_BIOGENESIS_AND_MAINTENANCE</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_PROTEIN_DNA_COMPLEX_ORGANIZATION</t>
-  </si>
-  <si>
-    <t>GOBP_PROTEIN_DNA_COMPLEX_ORGANIZATION</t>
-  </si>
-  <si>
-    <t>Hallmark|HALLMARK_E2F_TARGETS</t>
-  </si>
-  <si>
-    <t>HALLMARK_E2F_TARGETS</t>
+    <t>Reactome|REACTOME_RESPIRATORY_ELECTRON_TRANSPORT</t>
+  </si>
+  <si>
+    <t>REACTOME_RESPIRATORY_ELECTRON_TRANSPORT</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_ATP_SYNTHESIS_COUPLED_ELECTRON_TRANSPORT</t>
+  </si>
+  <si>
+    <t>GOBP_ATP_SYNTHESIS_COUPLED_ELECTRON_TRANSPORT</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_PROTEIN_MODIFICATION_BY_SMALL_PROTEIN_REMOVAL</t>
+  </si>
+  <si>
+    <t>GOBP_PROTEIN_MODIFICATION_BY_SMALL_PROTEIN_REMOVAL</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_RIBOSE_PHOSPHATE_BIOSYNTHETIC_PROCESS</t>
+  </si>
+  <si>
+    <t>GOBP_RIBOSE_PHOSPHATE_BIOSYNTHETIC_PROCESS</t>
   </si>
   <si>
     <t>pi</t>
@@ -308,19 +278,19 @@
     <t>label</t>
   </si>
   <si>
-    <t>SYNE2</t>
+    <t>MRPL13</t>
+  </si>
+  <si>
+    <t>MLYCD</t>
+  </si>
+  <si>
+    <t>MYH4</t>
   </si>
   <si>
     <t>DHCR24</t>
   </si>
   <si>
-    <t>MYH6</t>
-  </si>
-  <si>
-    <t>LMAN2</t>
-  </si>
-  <si>
-    <t>MYH4</t>
+    <t>PURA</t>
   </si>
   <si>
     <t>DCAF8</t>
@@ -329,13 +299,13 @@
     <t>PRPSAP2</t>
   </si>
   <si>
-    <t>MRPL44</t>
-  </si>
-  <si>
-    <t>NMT1</t>
-  </si>
-  <si>
-    <t>PITPNA</t>
+    <t>TMED9</t>
+  </si>
+  <si>
+    <t>LAMTOR2</t>
+  </si>
+  <si>
+    <t>CA14</t>
   </si>
   <si>
     <t>input</t>
@@ -353,7 +323,7 @@
     <t>03_Pathway_Enrichment/02_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>841ce5c33d7d681dc5b57e1380b1511a</t>
+    <t>33ee3e4f1fc7fd0e2b272761fb142497</t>
   </si>
   <si>
     <t>package</t>
@@ -974,7 +944,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -1017,10 +987,10 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>1.922830947004083</v>
+        <v>2.223438154103358</v>
       </c>
       <c r="G2">
-        <v>0.0009392615339380319</v>
+        <v>2.204000545155774E-07</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1040,10 +1010,10 @@
         <v>23</v>
       </c>
       <c r="F3">
-        <v>-2.205679591575138</v>
+        <v>2.294093664576923</v>
       </c>
       <c r="G3">
-        <v>0.001620795671127012</v>
+        <v>1.000579483299053E-05</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1063,10 +1033,10 @@
         <v>26</v>
       </c>
       <c r="F4">
-        <v>-1.778816272241438</v>
+        <v>2.296974201874169</v>
       </c>
       <c r="G4">
-        <v>0.001620795671127012</v>
+        <v>1.032907365068851E-05</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1080,16 +1050,16 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>1.742860964748822</v>
+        <v>1.857610860599793</v>
       </c>
       <c r="G5">
-        <v>0.001620795671127012</v>
+        <v>2.028833723511387E-05</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1100,19 +1070,19 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>1.971252328571465</v>
+        <v>-1.847626161050917</v>
       </c>
       <c r="G6">
-        <v>0.002362528719298489</v>
+        <v>9.477954655334876E-05</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1123,19 +1093,19 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>1.822786680677594</v>
+        <v>1.962603981722645</v>
       </c>
       <c r="G7">
-        <v>0.002582628250670707</v>
+        <v>9.649932178908133E-05</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1146,19 +1116,19 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
         <v>36</v>
       </c>
       <c r="F8">
-        <v>1.968592451316155</v>
+        <v>2.107810326762888</v>
       </c>
       <c r="G8">
-        <v>0.002582628250670707</v>
+        <v>0.0001956780311977285</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1172,16 +1142,16 @@
         <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
       </c>
       <c r="F9">
-        <v>-2.131972030148518</v>
+        <v>1.993140768794571</v>
       </c>
       <c r="G9">
-        <v>0.004992805620161343</v>
+        <v>0.0004531775939597876</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1201,10 +1171,10 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>-2.079618940513422</v>
+        <v>-2.876682451705756</v>
       </c>
       <c r="G10">
-        <v>2.617868211812181E-05</v>
+        <v>5.502141007854823E-18</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1215,19 +1185,19 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F11">
-        <v>2.415538364447673</v>
+        <v>-2.698555424367661</v>
       </c>
       <c r="G11">
-        <v>0.0001713383781427906</v>
+        <v>4.347589939072868E-14</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1238,19 +1208,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F12">
-        <v>2.182682340654037</v>
+        <v>-2.298704853975929</v>
       </c>
       <c r="G12">
-        <v>0.0003853671400157324</v>
+        <v>8.924608025548342E-11</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1261,19 +1231,19 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F13">
-        <v>-2.225547943750621</v>
+        <v>-2.488781421719434</v>
       </c>
       <c r="G13">
-        <v>0.0005367672018625347</v>
+        <v>1.78867830749479E-08</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1284,19 +1254,19 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F14">
-        <v>1.965241800258422</v>
+        <v>-2.274361794309991</v>
       </c>
       <c r="G14">
-        <v>0.0007789933225946364</v>
+        <v>1.162995724893067E-07</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1307,19 +1277,19 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="F15">
-        <v>1.767240425910248</v>
+        <v>-2.004896078364329</v>
       </c>
       <c r="G15">
-        <v>0.0007789933225946364</v>
+        <v>1.564911971820212E-07</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1333,16 +1303,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
         <v>49</v>
       </c>
       <c r="F16">
-        <v>2.212372973057348</v>
+        <v>-2.412185028159527</v>
       </c>
       <c r="G16">
-        <v>0.0009177593092511246</v>
+        <v>4.726701276803844E-06</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1353,47 +1323,47 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F17">
-        <v>-1.867875633582645</v>
+        <v>-2.315979167655824</v>
       </c>
       <c r="G17">
-        <v>0.001147386988611826</v>
+        <v>7.070719769246177E-05</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18">
-        <v>2.95934921412453</v>
+        <v>2.709504661693904</v>
       </c>
       <c r="G18">
-        <v>2.183051380974431E-17</v>
+        <v>4.276340400887096E-13</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
@@ -1408,61 +1378,61 @@
         <v>20</v>
       </c>
       <c r="F19">
-        <v>2.733474006643925</v>
+        <v>2.547303396537641</v>
       </c>
       <c r="G19">
-        <v>2.16371469263983E-14</v>
+        <v>1.614911668909311E-11</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F20">
-        <v>2.321477541137155</v>
+        <v>2.180453338082554</v>
       </c>
       <c r="G20">
-        <v>4.247905576961022E-10</v>
+        <v>2.719319752012218E-08</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="F21">
-        <v>2.651376942768429</v>
+        <v>2.376103645950848</v>
       </c>
       <c r="G21">
-        <v>4.622223771869755E-10</v>
+        <v>1.657400893679391E-06</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
@@ -1477,15 +1447,15 @@
         <v>54</v>
       </c>
       <c r="F22">
-        <v>2.562773830881384</v>
+        <v>2.391323288827733</v>
       </c>
       <c r="G22">
-        <v>2.432587536402038E-08</v>
+        <v>2.682312539965037E-06</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
@@ -1494,435 +1464,435 @@
         <v>55</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
         <v>56</v>
       </c>
       <c r="F23">
-        <v>2.504544990978771</v>
+        <v>-2.449529678607482</v>
       </c>
       <c r="G23">
-        <v>8.241978011120795E-08</v>
+        <v>3.787880339159282E-05</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F24">
-        <v>2.125933982878329</v>
+        <v>2.006220421432038</v>
       </c>
       <c r="G24">
-        <v>3.409607408043603E-06</v>
+        <v>0.0001521983888764684</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F25">
-        <v>2.452331306037554</v>
+        <v>-1.91644554320839</v>
       </c>
       <c r="G25">
-        <v>1.205456025696328E-05</v>
+        <v>0.0002160195340481075</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>60</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="s">
         <v>61</v>
       </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="s">
-        <v>62</v>
-      </c>
-      <c r="D26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" t="s">
-        <v>63</v>
-      </c>
       <c r="F26">
-        <v>-2.266395297014115</v>
+        <v>2.146768268223328</v>
       </c>
       <c r="G26">
-        <v>0.0007342208629109633</v>
+        <v>0.020334180872511</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="F27">
-        <v>1.872968984269439</v>
+        <v>-2.023043539718842</v>
       </c>
       <c r="G27">
-        <v>0.001265656759006333</v>
+        <v>0.03486707994350972</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
         <v>16</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F28">
-        <v>-2.233305573982406</v>
+        <v>2.541264407744438</v>
       </c>
       <c r="G28">
-        <v>0.001265656759006333</v>
+        <v>5.462993779452369E-09</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
         <v>19</v>
       </c>
       <c r="E29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F29">
-        <v>-2.194537608930866</v>
+        <v>2.687033962204581</v>
       </c>
       <c r="G29">
-        <v>0.001280151029482665</v>
+        <v>5.462993779452369E-09</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="F30">
-        <v>-2.0312557834771</v>
+        <v>-2.329272839692229</v>
       </c>
       <c r="G30">
-        <v>0.00166096266887517</v>
+        <v>1.111742409500044E-08</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>2.088611555973001</v>
+        <v>-2.287233913804879</v>
       </c>
       <c r="G31">
-        <v>0.002165058669721533</v>
+        <v>1.423267156052321E-08</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
         <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F32">
-        <v>-1.96043687585336</v>
+        <v>2.607573486622292</v>
       </c>
       <c r="G32">
-        <v>0.002720521560897575</v>
+        <v>2.002657115237939E-08</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F33">
-        <v>1.861208256556141</v>
+        <v>-2.158936700910642</v>
       </c>
       <c r="G33">
-        <v>0.003537531159181445</v>
+        <v>2.724884121778048E-08</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="F34">
-        <v>-2.70325233650312</v>
+        <v>2.446440543636506</v>
       </c>
       <c r="G34">
-        <v>1.110605771141992E-13</v>
+        <v>4.824441629552877E-08</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" t="s">
         <v>74</v>
       </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" t="s">
-        <v>32</v>
-      </c>
-      <c r="E35" t="s">
-        <v>33</v>
-      </c>
       <c r="F35">
-        <v>-2.674133990960637</v>
+        <v>2.603873856276907</v>
       </c>
       <c r="G35">
-        <v>7.969410051541603E-13</v>
+        <v>6.484596575223832E-07</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F36">
-        <v>-2.421084530989954</v>
+        <v>2.263470331743567</v>
       </c>
       <c r="G36">
-        <v>3.644553662550022E-12</v>
+        <v>8.18958171174307E-05</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E37" t="s">
-        <v>76</v>
+        <v>23</v>
       </c>
       <c r="F37">
-        <v>2.55879335657243</v>
+        <v>2.220574971624452</v>
       </c>
       <c r="G37">
-        <v>1.494781610698376E-08</v>
+        <v>8.740337316301052E-05</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="D38" t="s">
         <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="F38">
-        <v>2.532524597093251</v>
+        <v>2.150649603666256</v>
       </c>
       <c r="G38">
-        <v>1.761375726359192E-08</v>
+        <v>8.740337316301052E-05</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
         <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F39">
-        <v>2.43151112662734</v>
+        <v>2.196944105999707</v>
       </c>
       <c r="G39">
-        <v>1.787864261462889E-08</v>
+        <v>0.0002038255810325809</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F40">
-        <v>2.405964828605525</v>
+        <v>-2.319975522598562</v>
       </c>
       <c r="G40">
-        <v>3.37116643933149E-07</v>
+        <v>0.0002038255810325809</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F41">
-        <v>-2.219384971557113</v>
+        <v>2.385917799479357</v>
       </c>
       <c r="G41">
-        <v>9.598296788220887E-07</v>
+        <v>0.0002038255810325809</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
@@ -1937,539 +1907,263 @@
         <v>83</v>
       </c>
       <c r="F42">
-        <v>2.284819080381068</v>
+        <v>1.948904619304577</v>
       </c>
       <c r="G42">
-        <v>0.00189731922998138</v>
+        <v>0.001163623026353623</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D43" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E43" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F43">
-        <v>2.255370810098372</v>
+        <v>2.148497302041234</v>
       </c>
       <c r="G43">
-        <v>0.00189731922998138</v>
+        <v>0.002523603436892047</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E44" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="F44">
-        <v>2.304638948000209</v>
+        <v>2.709504661693904</v>
       </c>
       <c r="G44">
-        <v>0.00189731922998138</v>
+        <v>4.276340400887096E-13</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C45" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
         <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F45">
-        <v>-2.207161849672367</v>
+        <v>2.547303396537641</v>
       </c>
       <c r="G45">
-        <v>0.002660464418803695</v>
+        <v>1.614911668909311E-11</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F46">
-        <v>1.856365111021561</v>
+        <v>2.180453338082554</v>
       </c>
       <c r="G46">
-        <v>0.003064985254031235</v>
+        <v>2.719319752012218E-08</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E47" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="F47">
-        <v>-1.978825835042164</v>
+        <v>2.376103645950848</v>
       </c>
       <c r="G47">
-        <v>0.003473131706371204</v>
+        <v>1.657400893679391E-06</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="F48">
-        <v>2.189805530107555</v>
+        <v>2.391323288827733</v>
       </c>
       <c r="G48">
-        <v>0.003702689916046316</v>
+        <v>2.682312539965037E-06</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="F49">
-        <v>1.980520579469523</v>
+        <v>-2.449529678607482</v>
       </c>
       <c r="G49">
-        <v>0.02032128440669566</v>
+        <v>3.787880339159282E-05</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F50">
-        <v>2.95934921412453</v>
+        <v>2.006220421432038</v>
       </c>
       <c r="G50">
-        <v>2.183051380974431E-17</v>
+        <v>0.0001521983888764684</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C51" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E51" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="F51">
-        <v>2.733474006643925</v>
+        <v>-1.91644554320839</v>
       </c>
       <c r="G51">
-        <v>2.16371469263983E-14</v>
+        <v>0.0002160195340481075</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
         <v>22</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F52">
-        <v>2.321477541137155</v>
+        <v>2.146768268223328</v>
       </c>
       <c r="G52">
-        <v>4.247905576961022E-10</v>
+        <v>0.020334180872511</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="D53" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="F53">
-        <v>2.651376942768429</v>
+        <v>-2.023043539718842</v>
       </c>
       <c r="G53">
-        <v>4.622223771869755E-10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" t="s">
-        <v>53</v>
-      </c>
-      <c r="D54" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" t="s">
-        <v>54</v>
-      </c>
-      <c r="F54">
-        <v>2.562773830881384</v>
-      </c>
-      <c r="G54">
-        <v>2.432587536402038E-08</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" t="s">
-        <v>55</v>
-      </c>
-      <c r="D55" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" t="s">
-        <v>56</v>
-      </c>
-      <c r="F55">
-        <v>2.504544990978771</v>
-      </c>
-      <c r="G55">
-        <v>8.241978011120795E-08</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" t="s">
-        <v>50</v>
-      </c>
-      <c r="B56" t="s">
-        <v>94</v>
-      </c>
-      <c r="C56" t="s">
-        <v>57</v>
-      </c>
-      <c r="D56" t="s">
-        <v>22</v>
-      </c>
-      <c r="E56" t="s">
-        <v>58</v>
-      </c>
-      <c r="F56">
-        <v>2.125933982878329</v>
-      </c>
-      <c r="G56">
-        <v>3.409607408043603E-06</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" t="s">
-        <v>50</v>
-      </c>
-      <c r="B57" t="s">
-        <v>94</v>
-      </c>
-      <c r="C57" t="s">
-        <v>59</v>
-      </c>
-      <c r="D57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57">
-        <v>2.452331306037554</v>
-      </c>
-      <c r="G57">
-        <v>1.205456025696328E-05</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" t="s">
-        <v>94</v>
-      </c>
-      <c r="C58" t="s">
-        <v>62</v>
-      </c>
-      <c r="D58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" t="s">
-        <v>63</v>
-      </c>
-      <c r="F58">
-        <v>-2.266395297014115</v>
-      </c>
-      <c r="G58">
-        <v>0.0007342208629109633</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" t="s">
-        <v>61</v>
-      </c>
-      <c r="B59" t="s">
-        <v>94</v>
-      </c>
-      <c r="C59" t="s">
-        <v>31</v>
-      </c>
-      <c r="D59" t="s">
-        <v>32</v>
-      </c>
-      <c r="E59" t="s">
-        <v>33</v>
-      </c>
-      <c r="F59">
-        <v>1.872968984269439</v>
-      </c>
-      <c r="G59">
-        <v>0.001265656759006333</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" t="s">
-        <v>64</v>
-      </c>
-      <c r="D60" t="s">
-        <v>19</v>
-      </c>
-      <c r="E60" t="s">
-        <v>65</v>
-      </c>
-      <c r="F60">
-        <v>-2.233305573982406</v>
-      </c>
-      <c r="G60">
-        <v>0.001265656759006333</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" t="s">
-        <v>61</v>
-      </c>
-      <c r="B61" t="s">
-        <v>94</v>
-      </c>
-      <c r="C61" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" t="s">
-        <v>19</v>
-      </c>
-      <c r="E61" t="s">
-        <v>67</v>
-      </c>
-      <c r="F61">
-        <v>-2.194537608930866</v>
-      </c>
-      <c r="G61">
-        <v>0.001280151029482665</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" t="s">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>94</v>
-      </c>
-      <c r="C62" t="s">
-        <v>68</v>
-      </c>
-      <c r="D62" t="s">
-        <v>19</v>
-      </c>
-      <c r="E62" t="s">
-        <v>69</v>
-      </c>
-      <c r="F62">
-        <v>-2.0312557834771</v>
-      </c>
-      <c r="G62">
-        <v>0.00166096266887517</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7">
-      <c r="A63" t="s">
-        <v>61</v>
-      </c>
-      <c r="B63" t="s">
-        <v>94</v>
-      </c>
-      <c r="C63" t="s">
-        <v>70</v>
-      </c>
-      <c r="D63" t="s">
-        <v>22</v>
-      </c>
-      <c r="E63" t="s">
-        <v>71</v>
-      </c>
-      <c r="F63">
-        <v>2.088611555973001</v>
-      </c>
-      <c r="G63">
-        <v>0.002165058669721533</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" t="s">
-        <v>61</v>
-      </c>
-      <c r="B64" t="s">
-        <v>94</v>
-      </c>
-      <c r="C64" t="s">
-        <v>72</v>
-      </c>
-      <c r="D64" t="s">
-        <v>19</v>
-      </c>
-      <c r="E64" t="s">
-        <v>73</v>
-      </c>
-      <c r="F64">
-        <v>-1.96043687585336</v>
-      </c>
-      <c r="G64">
-        <v>0.002720521560897575</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65" t="s">
-        <v>94</v>
-      </c>
-      <c r="C65" t="s">
-        <v>53</v>
-      </c>
-      <c r="D65" t="s">
-        <v>19</v>
-      </c>
-      <c r="E65" t="s">
-        <v>54</v>
-      </c>
-      <c r="F65">
-        <v>1.861208256556141</v>
-      </c>
-      <c r="G65">
-        <v>0.003537531159181445</v>
+        <v>0.03486707994350972</v>
       </c>
     </row>
   </sheetData>
@@ -2490,117 +2184,117 @@
         <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
         <v>94</v>
-      </c>
-      <c r="C10" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -2615,24 +2309,24 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2647,409 +2341,409 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C15" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C24" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C31" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B32" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C33" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C36" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/03_Pathway_Enrichment/05_Volcano/c_data/05_volcano.xlsx
+++ b/03_Pathway_Enrichment/05_Volcano/c_data/05_volcano.xlsx
@@ -323,7 +323,7 @@
     <t>03_Pathway_Enrichment/02_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>33ee3e4f1fc7fd0e2b272761fb142497</t>
+    <t>f033bd0788b25034f66ba348bed647ab</t>
   </si>
   <si>
     <t>package</t>

--- a/03_Pathway_Enrichment/05_Volcano/c_data/05_volcano.xlsx
+++ b/03_Pathway_Enrichment/05_Volcano/c_data/05_volcano.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="191">
   <si>
     <t>sheet</t>
   </si>
@@ -83,22 +83,49 @@
     <t>REACTOME_AEROBIC_RESPIRATION_AND_RESPIRATORY_ELECTRON_TRANSPORT</t>
   </si>
   <si>
+    <t>KEGG_Legacy|KEGG_PARKINSONS_DISEASE</t>
+  </si>
+  <si>
+    <t>KEGG_Legacy</t>
+  </si>
+  <si>
+    <t>KEGG_PARKINSONS_DISEASE</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_OXIDATIVE_PHOSPHORYLATION</t>
+  </si>
+  <si>
+    <t>GOBP</t>
+  </si>
+  <si>
+    <t>GOBP_OXIDATIVE_PHOSPHORYLATION GOBP</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_RESPIRATORY_ELECTRON_TRANSPORT</t>
+  </si>
+  <si>
+    <t>REACTOME_RESPIRATORY_ELECTRON_TRANSPORT</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_CELLULAR_RESPIRATION</t>
+  </si>
+  <si>
+    <t>GOBP_CELLULAR_RESPIRATION</t>
+  </si>
+  <si>
     <t>GOBP|GOBP_PROTON_TRANSMEMBRANE_TRANSPORT</t>
   </si>
   <si>
-    <t>GOBP</t>
-  </si>
-  <si>
     <t>GOBP_PROTON_TRANSMEMBRANE_TRANSPORT</t>
   </si>
   <si>
-    <t>KEGG_Legacy|KEGG_PARKINSONS_DISEASE</t>
-  </si>
-  <si>
-    <t>KEGG_Legacy</t>
-  </si>
-  <si>
-    <t>KEGG_PARKINSONS_DISEASE</t>
+    <t>Hallmark|HALLMARK_OXIDATIVE_PHOSPHORYLATION</t>
+  </si>
+  <si>
+    <t>Hallmark</t>
+  </si>
+  <si>
+    <t>HALLMARK_OXIDATIVE_PHOSPHORYLATION Hallmark</t>
   </si>
   <si>
     <t>GO_Slim|TRANSMEMBRANE_TRANSPORT</t>
@@ -110,79 +137,148 @@
     <t>transmembrane transport</t>
   </si>
   <si>
-    <t>GO_Slim|CYTOSKELETON_ORGANIZATION</t>
-  </si>
-  <si>
-    <t>cytoskeleton organization</t>
-  </si>
-  <si>
-    <t>Hallmark|HALLMARK_OXIDATIVE_PHOSPHORYLATION</t>
-  </si>
-  <si>
-    <t>Hallmark</t>
+    <t>Acute_Interaction</t>
   </si>
   <si>
     <t>HALLMARK_OXIDATIVE_PHOSPHORYLATION</t>
   </si>
   <si>
-    <t>KEGG_Legacy|KEGG_ALZHEIMERS_DISEASE</t>
-  </si>
-  <si>
-    <t>KEGG_ALZHEIMERS_DISEASE</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_NUCLEOTIDE_BIOSYNTHETIC_PROCESS</t>
-  </si>
-  <si>
-    <t>GOBP_NUCLEOTIDE_BIOSYNTHETIC_PROCESS</t>
-  </si>
-  <si>
-    <t>Acute_Interaction</t>
-  </si>
-  <si>
     <t>GOBP|GOBP_GENERATION_OF_PRECURSOR_METABOLITES_AND_ENERGY</t>
   </si>
   <si>
     <t>GOBP_GENERATION_OF_PRECURSOR_METABOLITES_AND_ENERGY</t>
   </si>
   <si>
+    <t>GOBP|GOBP_MITOCHONDRION_ORGANIZATION</t>
+  </si>
+  <si>
+    <t>GOBP_MITOCHONDRION_ORGANIZATION</t>
+  </si>
+  <si>
+    <t>GO_Slim|NUCLEOBASE_CONTAINING_SMALL_MOLECULE_METABOLIC_PROCESS</t>
+  </si>
+  <si>
+    <t>nucleobase-containing small molecule metabolic process</t>
+  </si>
+  <si>
+    <t>GO_Slim|VESICLE_MEDIATED_TRANSPORT</t>
+  </si>
+  <si>
+    <t>vesicle-mediated transport</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_MITOCHONDRIAL_RESPIRATORY_CHAIN_COMPLEX_ASSEMBLY</t>
+  </si>
+  <si>
+    <t>GOBP_MITOCHONDRIAL_RESPIRATORY_CHAIN_COMPLEX_ASSEMBLY</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_MITOCHONDRIAL_PROTEIN_DEGRADATION</t>
+  </si>
+  <si>
+    <t>REACTOME_MITOCHONDRIAL_PROTEIN_DEGRADATION</t>
+  </si>
+  <si>
+    <t>Training_HR</t>
+  </si>
+  <si>
     <t>KEGG_Legacy|KEGG_HUNTINGTONS_DISEASE</t>
   </si>
   <si>
     <t>KEGG_HUNTINGTONS_DISEASE</t>
   </si>
   <si>
-    <t>GOBP|GOBP_MITOCHONDRION_ORGANIZATION</t>
-  </si>
-  <si>
-    <t>GOBP_MITOCHONDRION_ORGANIZATION</t>
-  </si>
-  <si>
-    <t>GO_Slim|NUCLEOBASE_CONTAINING_SMALL_MOLECULE_METABOLIC_PROCESS</t>
-  </si>
-  <si>
-    <t>nucleobase-containing small molecule metabolic process</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_MITOCHONDRIAL_RESPIRATORY_CHAIN_COMPLEX_ASSEMBLY</t>
-  </si>
-  <si>
-    <t>GOBP_MITOCHONDRIAL_RESPIRATORY_CHAIN_COMPLEX_ASSEMBLY</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_MITOCHONDRIAL_MEMBRANE_ORGANIZATION</t>
-  </si>
-  <si>
-    <t>GOBP_MITOCHONDRIAL_MEMBRANE_ORGANIZATION</t>
-  </si>
-  <si>
-    <t>Training_HR</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_MITOCHONDRIAL_PROTEIN_DEGRADATION</t>
-  </si>
-  <si>
-    <t>REACTOME_MITOCHONDRIAL_PROTEIN_DEGRADATION</t>
+    <t>Reactome|REACTOME_PROTEIN_LOCALIZATION</t>
+  </si>
+  <si>
+    <t>REACTOME_PROTEIN_LOCALIZATION</t>
+  </si>
+  <si>
+    <t>Training_LR</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_REGULATION_OF_MUSCLE_CONTRACTION</t>
+  </si>
+  <si>
+    <t>GOBP_REGULATION_OF_MUSCLE_CONTRACTION</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_CLEC7A_DECTIN_1_SIGNALING</t>
+  </si>
+  <si>
+    <t>REACTOME_CLEC7A_DECTIN_1_SIGNALING</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_MUSCLE_CONTRACTION</t>
+  </si>
+  <si>
+    <t>GOBP_MUSCLE_CONTRACTION</t>
+  </si>
+  <si>
+    <t>KEGG_Legacy|KEGG_CALCIUM_SIGNALING_PATHWAY</t>
+  </si>
+  <si>
+    <t>KEGG_CALCIUM_SIGNALING_PATHWAY</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_SIGNALING_BY_NOTCH</t>
+  </si>
+  <si>
+    <t>REACTOME_SIGNALING_BY_NOTCH</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_CARDIAC_MUSCLE_CONTRACTION</t>
+  </si>
+  <si>
+    <t>GOBP_CARDIAC_MUSCLE_CONTRACTION</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_HEDGEHOG_ON_STATE</t>
+  </si>
+  <si>
+    <t>REACTOME_HEDGEHOG_ON_STATE</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_RIBOSOME_QUALITY_CONTROL_RQC_COMPLEX_EXTRACTS_AND_DEGRADES_NASCENT_PEPTIDE</t>
+  </si>
+  <si>
+    <t>REACTOME_RIBOSOME_QUALITY_CONTROL_RQC_COMPLEX_EXTRACTS_AND_DEGRADES_NASCENT_PEPTIDE</t>
+  </si>
+  <si>
+    <t>Acute_HR</t>
+  </si>
+  <si>
+    <t>GO_Slim|CYTOPLASMIC_TRANSLATION</t>
+  </si>
+  <si>
+    <t>cytoplasmic translation</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_EUKARYOTIC_TRANSLATION_ELONGATION</t>
+  </si>
+  <si>
+    <t>REACTOME_EUKARYOTIC_TRANSLATION_ELONGATION</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_DENGUE_VIRUS_INFECTION</t>
+  </si>
+  <si>
+    <t>REACTOME_DENGUE_VIRUS_INFECTION</t>
+  </si>
+  <si>
+    <t>GO_Slim|MRNA_METABOLIC_PROCESS</t>
+  </si>
+  <si>
+    <t>mRNA metabolic process</t>
+  </si>
+  <si>
+    <t>Reactome|REACTOME_MRNA_3_END_PROCESSING</t>
+  </si>
+  <si>
+    <t>REACTOME_MRNA_3_END_PROCESSING</t>
+  </si>
+  <si>
+    <t>Acute_LR</t>
   </si>
   <si>
     <t>Reactome|REACTOME_STRIATED_MUSCLE_CONTRACTION</t>
@@ -191,85 +287,28 @@
     <t>REACTOME_STRIATED_MUSCLE_CONTRACTION</t>
   </si>
   <si>
-    <t>GO_Slim|MUSCLE_SYSTEM_PROCESS</t>
-  </si>
-  <si>
-    <t>muscle system process</t>
-  </si>
-  <si>
-    <t>Training_LR</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_TRICARBOXYLIC_ACID_CYCLE</t>
-  </si>
-  <si>
-    <t>GOBP_TRICARBOXYLIC_ACID_CYCLE</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_SIGNALING_BY_NOTCH</t>
-  </si>
-  <si>
-    <t>REACTOME_SIGNALING_BY_NOTCH</t>
-  </si>
-  <si>
-    <t>Acute_HR</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_CYTOPLASMIC_TRANSLATION</t>
-  </si>
-  <si>
-    <t>GOBP_CYTOPLASMIC_TRANSLATION</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_EUKARYOTIC_TRANSLATION_ELONGATION</t>
-  </si>
-  <si>
-    <t>REACTOME_EUKARYOTIC_TRANSLATION_ELONGATION</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_NONSENSE_MEDIATED_DECAY_NMD</t>
-  </si>
-  <si>
-    <t>REACTOME_NONSENSE_MEDIATED_DECAY_NMD</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_DENGUE_VIRUS_INFECTION</t>
-  </si>
-  <si>
-    <t>REACTOME_DENGUE_VIRUS_INFECTION</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_NEGATIVE_REGULATION_OF_SYNCYTIUM_FORMATION_BY_PLASMA_MEMBRANE_FUSION</t>
-  </si>
-  <si>
-    <t>GOBP_NEGATIVE_REGULATION_OF_SYNCYTIUM_FORMATION_BY_PLASMA_MEMBRANE_FUSION</t>
-  </si>
-  <si>
-    <t>Acute_LR</t>
-  </si>
-  <si>
-    <t>Reactome|REACTOME_RESPIRATORY_ELECTRON_TRANSPORT</t>
-  </si>
-  <si>
-    <t>REACTOME_RESPIRATORY_ELECTRON_TRANSPORT</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_ATP_SYNTHESIS_COUPLED_ELECTRON_TRANSPORT</t>
-  </si>
-  <si>
-    <t>GOBP_ATP_SYNTHESIS_COUPLED_ELECTRON_TRANSPORT</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_PROTEIN_MODIFICATION_BY_SMALL_PROTEIN_REMOVAL</t>
-  </si>
-  <si>
-    <t>GOBP_PROTEIN_MODIFICATION_BY_SMALL_PROTEIN_REMOVAL</t>
-  </si>
-  <si>
-    <t>GOBP|GOBP_RIBOSE_PHOSPHATE_BIOSYNTHETIC_PROCESS</t>
-  </si>
-  <si>
-    <t>GOBP_RIBOSE_PHOSPHATE_BIOSYNTHETIC_PROCESS</t>
+    <t>GOBP|GOBP_CELLULAR_COMPONENT_ASSEMBLY_INVOLVED_IN_MORPHOGENESIS</t>
+  </si>
+  <si>
+    <t>GOBP_CELLULAR_COMPONENT_ASSEMBLY_INVOLVED_IN_MORPHOGENESIS</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_STRIATED_MUSCLE_CELL_DIFFERENTIATION</t>
+  </si>
+  <si>
+    <t>GOBP_STRIATED_MUSCLE_CELL_DIFFERENTIATION</t>
+  </si>
+  <si>
+    <t>GOBP|GOBP_PROTEIN_DNA_COMPLEX_ORGANIZATION</t>
+  </si>
+  <si>
+    <t>GOBP_PROTEIN_DNA_COMPLEX_ORGANIZATION</t>
+  </si>
+  <si>
+    <t>KEGG_Legacy|KEGG_RIBOSOME</t>
+  </si>
+  <si>
+    <t>KEGG_RIBOSOME</t>
   </si>
   <si>
     <t>pi</t>
@@ -278,28 +317,22 @@
     <t>label</t>
   </si>
   <si>
-    <t>MRPL13</t>
-  </si>
-  <si>
-    <t>MLYCD</t>
+    <t>ACTBL2</t>
+  </si>
+  <si>
+    <t>NUBP2</t>
   </si>
   <si>
     <t>MYH4</t>
   </si>
   <si>
-    <t>DHCR24</t>
-  </si>
-  <si>
-    <t>PURA</t>
-  </si>
-  <si>
-    <t>DCAF8</t>
-  </si>
-  <si>
-    <t>PRPSAP2</t>
-  </si>
-  <si>
-    <t>TMED9</t>
+    <t>LMAN2</t>
+  </si>
+  <si>
+    <t>TOMM40</t>
+  </si>
+  <si>
+    <t>AKT2</t>
   </si>
   <si>
     <t>LAMTOR2</t>
@@ -308,6 +341,12 @@
     <t>CA14</t>
   </si>
   <si>
+    <t>COX20</t>
+  </si>
+  <si>
+    <t>PFKFB2</t>
+  </si>
+  <si>
     <t>input</t>
   </si>
   <si>
@@ -323,7 +362,7 @@
     <t>03_Pathway_Enrichment/02_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>f033bd0788b25034f66ba348bed647ab</t>
+    <t>52c365ae84d1f5f25d3e280360d861dd</t>
   </si>
   <si>
     <t>package</t>
@@ -944,7 +983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
@@ -987,10 +1026,10 @@
         <v>20</v>
       </c>
       <c r="F2">
-        <v>2.223438154103358</v>
+        <v>2.471193818524374</v>
       </c>
       <c r="G2">
-        <v>2.204000545155774E-07</v>
+        <v>1.526914392889979E-10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1010,10 +1049,10 @@
         <v>23</v>
       </c>
       <c r="F3">
-        <v>2.294093664576923</v>
+        <v>2.616638122666611</v>
       </c>
       <c r="G3">
-        <v>1.000579483299053E-05</v>
+        <v>6.108344044579076E-09</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1033,10 +1072,10 @@
         <v>26</v>
       </c>
       <c r="F4">
-        <v>2.296974201874169</v>
+        <v>2.486689669624205</v>
       </c>
       <c r="G4">
-        <v>1.032907365068851E-05</v>
+        <v>2.723175176426457E-08</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1050,16 +1089,16 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
       <c r="F5">
-        <v>1.857610860599793</v>
+        <v>2.450240062373804</v>
       </c>
       <c r="G5">
-        <v>2.028833723511387E-05</v>
+        <v>2.723175176426457E-08</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1070,19 +1109,19 @@
         <v>16</v>
       </c>
       <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
       <c r="F6">
-        <v>-1.847626161050917</v>
+        <v>2.179173836188318</v>
       </c>
       <c r="G6">
-        <v>9.477954655334876E-05</v>
+        <v>3.209321554568521E-08</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1093,19 +1132,19 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>34</v>
-      </c>
       <c r="F7">
-        <v>1.962603981722645</v>
+        <v>2.49604420117308</v>
       </c>
       <c r="G7">
-        <v>9.649932178908133E-05</v>
+        <v>3.209321554568521E-08</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1116,19 +1155,19 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
         <v>35</v>
       </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
       <c r="F8">
-        <v>2.107810326762888</v>
+        <v>2.246725541894552</v>
       </c>
       <c r="G8">
-        <v>0.0001956780311977285</v>
+        <v>6.101894183451595E-08</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1139,19 +1178,19 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
         <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>22</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
       </c>
       <c r="F9">
-        <v>1.993140768794571</v>
+        <v>2.048553897928656</v>
       </c>
       <c r="G9">
-        <v>0.0004531775939597876</v>
+        <v>6.706112378277686E-08</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1171,10 +1210,10 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <v>-2.876682451705756</v>
+        <v>-2.975287565562438</v>
       </c>
       <c r="G10">
-        <v>5.502141007854823E-18</v>
+        <v>3.572890323995531E-20</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1185,19 +1224,19 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F11">
-        <v>-2.698555424367661</v>
+        <v>-2.704942659417796</v>
       </c>
       <c r="G11">
-        <v>4.347589939072868E-14</v>
+        <v>6.180684256803332E-14</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1208,19 +1247,19 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12">
-        <v>-2.298704853975929</v>
+        <v>-2.394960391664755</v>
       </c>
       <c r="G12">
-        <v>8.924608025548342E-11</v>
+        <v>7.193620563080518E-13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1231,19 +1270,19 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F13">
-        <v>-2.488781421719434</v>
+        <v>-2.285789321313128</v>
       </c>
       <c r="G13">
-        <v>1.78867830749479E-08</v>
+        <v>4.118215678875391E-08</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1254,19 +1293,19 @@
         <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14">
-        <v>-2.274361794309991</v>
+        <v>-2.058333681131203</v>
       </c>
       <c r="G14">
-        <v>1.162995724893067E-07</v>
+        <v>8.998741039421503E-08</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1277,19 +1316,19 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F15">
-        <v>-2.004896078364329</v>
+        <v>2.054142151060112</v>
       </c>
       <c r="G15">
-        <v>1.564911971820212E-07</v>
+        <v>9.08401280209784E-08</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1300,19 +1339,19 @@
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F16">
-        <v>-2.412185028159527</v>
+        <v>-2.561356751681068</v>
       </c>
       <c r="G16">
-        <v>4.726701276803844E-06</v>
+        <v>8.564787436126561E-07</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1323,47 +1362,47 @@
         <v>16</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17">
-        <v>-2.315979167655824</v>
+        <v>-2.284301757698423</v>
       </c>
       <c r="G17">
-        <v>7.070719769246177E-05</v>
+        <v>1.879774406970555E-05</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F18">
-        <v>2.709504661693904</v>
+        <v>2.836022026499688</v>
       </c>
       <c r="G18">
-        <v>4.276340400887096E-13</v>
+        <v>3.987116232439306E-18</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
         <v>16</v>
@@ -1378,378 +1417,378 @@
         <v>20</v>
       </c>
       <c r="F19">
-        <v>2.547303396537641</v>
+        <v>2.727895477774346</v>
       </c>
       <c r="G19">
-        <v>1.614911668909311E-11</v>
+        <v>2.685361711395535E-15</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
         <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20">
-        <v>2.180453338082554</v>
+        <v>2.481725728377683</v>
       </c>
       <c r="G20">
-        <v>2.719319752012218E-08</v>
+        <v>9.119349579616228E-14</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
         <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F21">
-        <v>2.376103645950848</v>
+        <v>2.525910448327465</v>
       </c>
       <c r="G21">
-        <v>1.657400893679391E-06</v>
+        <v>5.795644104829686E-13</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22">
-        <v>2.391323288827733</v>
+        <v>2.534534244421963</v>
       </c>
       <c r="G22">
-        <v>2.682312539965037E-06</v>
+        <v>2.651466655900934E-09</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
         <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F23">
-        <v>-2.449529678607482</v>
+        <v>2.53949220083289</v>
       </c>
       <c r="G23">
-        <v>3.787880339159282E-05</v>
+        <v>4.713749000153153E-09</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
         <v>16</v>
       </c>
       <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" t="s">
         <v>44</v>
       </c>
-      <c r="D24" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" t="s">
-        <v>45</v>
-      </c>
       <c r="F24">
-        <v>2.006220421432038</v>
+        <v>2.301487125414149</v>
       </c>
       <c r="G24">
-        <v>0.0001521983888764684</v>
+        <v>2.468333499875939E-08</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
         <v>16</v>
       </c>
       <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
         <v>57</v>
       </c>
-      <c r="D25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" t="s">
-        <v>58</v>
-      </c>
       <c r="F25">
-        <v>-1.91644554320839</v>
+        <v>2.36340314333015</v>
       </c>
       <c r="G25">
-        <v>0.0002160195340481075</v>
+        <v>9.739869585976538E-07</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
         <v>59</v>
       </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
         <v>60</v>
       </c>
-      <c r="D26" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" t="s">
-        <v>61</v>
-      </c>
       <c r="F26">
-        <v>2.146768268223328</v>
+        <v>-2.229125916720378</v>
       </c>
       <c r="G26">
-        <v>0.020334180872511</v>
+        <v>0.00237939424016248</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" t="s">
         <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
         <v>19</v>
       </c>
       <c r="E27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F27">
-        <v>-2.023043539718842</v>
+        <v>-2.230840354268482</v>
       </c>
       <c r="G27">
-        <v>0.03486707994350972</v>
+        <v>0.002442898767015984</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" t="s">
         <v>64</v>
       </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" t="s">
-        <v>66</v>
-      </c>
       <c r="F28">
-        <v>2.541264407744438</v>
+        <v>-1.829026498962724</v>
       </c>
       <c r="G28">
-        <v>5.462993779452369E-09</v>
+        <v>0.003221328015687954</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F29">
-        <v>2.687033962204581</v>
+        <v>-2.109985236916042</v>
       </c>
       <c r="G29">
-        <v>5.462993779452369E-09</v>
+        <v>0.005345516941971719</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F30">
-        <v>-2.329272839692229</v>
+        <v>-2.110326195239017</v>
       </c>
       <c r="G30">
-        <v>1.111742409500044E-08</v>
+        <v>0.005345516941971719</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F31">
-        <v>-2.287233913804879</v>
+        <v>-1.968855916108449</v>
       </c>
       <c r="G31">
-        <v>1.423267156052321E-08</v>
+        <v>0.007274026530314413</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
         <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
         <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F32">
-        <v>2.607573486622292</v>
+        <v>-2.094233737590684</v>
       </c>
       <c r="G32">
-        <v>2.002657115237939E-08</v>
+        <v>0.007274026530314413</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
         <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="F33">
-        <v>-2.158936700910642</v>
+        <v>-1.882139490975687</v>
       </c>
       <c r="G33">
-        <v>2.724884121778048E-08</v>
+        <v>0.008148644524061697</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
         <v>16</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="F34">
-        <v>2.446440543636506</v>
+        <v>-2.637054003340127</v>
       </c>
       <c r="G34">
-        <v>4.824441629552877E-08</v>
+        <v>2.117002384840635E-13</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
       </c>
       <c r="C35" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F35">
-        <v>2.603873856276907</v>
+        <v>2.70422235699542</v>
       </c>
       <c r="G35">
-        <v>6.484596575223832E-07</v>
+        <v>1.426488867712942E-11</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1760,19 +1799,19 @@
         <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D36" t="s">
         <v>25</v>
       </c>
       <c r="E36" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F36">
-        <v>2.263470331743567</v>
+        <v>-2.370891175980851</v>
       </c>
       <c r="G36">
-        <v>8.18958171174307E-05</v>
+        <v>3.075597100832E-11</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1783,19 +1822,19 @@
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E37" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F37">
-        <v>2.220574971624452</v>
+        <v>-2.50056095594652</v>
       </c>
       <c r="G37">
-        <v>8.740337316301052E-05</v>
+        <v>5.085349351242583E-11</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1806,19 +1845,19 @@
         <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D38" t="s">
         <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F38">
-        <v>2.150649603666256</v>
+        <v>2.791008161933044</v>
       </c>
       <c r="G38">
-        <v>8.740337316301052E-05</v>
+        <v>5.085349351242583E-11</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1829,19 +1868,19 @@
         <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F39">
-        <v>2.196944105999707</v>
+        <v>2.57272634086135</v>
       </c>
       <c r="G39">
-        <v>0.0002038255810325809</v>
+        <v>8.920669905701235E-09</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1852,19 +1891,19 @@
         <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F40">
-        <v>-2.319975522598562</v>
+        <v>2.490904061841025</v>
       </c>
       <c r="G40">
-        <v>0.0002038255810325809</v>
+        <v>2.507764929294708E-08</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1875,295 +1914,571 @@
         <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="D41" t="s">
         <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="F41">
-        <v>2.385917799479357</v>
+        <v>2.685510176353903</v>
       </c>
       <c r="G41">
-        <v>0.0002038255810325809</v>
+        <v>3.284792745920008E-08</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
         <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E42" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F42">
-        <v>1.948904619304577</v>
+        <v>2.286896964112172</v>
       </c>
       <c r="G42">
-        <v>0.001163623026353623</v>
+        <v>4.359592105696738E-07</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="F43">
-        <v>2.148497302041234</v>
+        <v>2.770674246524893</v>
       </c>
       <c r="G43">
-        <v>0.002523603436892047</v>
+        <v>4.359592105696738E-07</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="F44">
-        <v>2.709504661693904</v>
+        <v>2.444346293707055</v>
       </c>
       <c r="G44">
-        <v>4.276340400887096E-13</v>
+        <v>9.041247469929029E-05</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="F45">
-        <v>2.547303396537641</v>
+        <v>2.054318232813715</v>
       </c>
       <c r="G45">
-        <v>1.614911668909311E-11</v>
+        <v>0.0001173993850723867</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="F46">
-        <v>2.180453338082554</v>
+        <v>2.487427273882168</v>
       </c>
       <c r="G46">
-        <v>2.719319752012218E-08</v>
+        <v>0.0002063818247555607</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E47" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="F47">
-        <v>2.376103645950848</v>
+        <v>2.211437421259997</v>
       </c>
       <c r="G47">
-        <v>1.657400893679391E-06</v>
+        <v>0.0002063818247555607</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E48" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F48">
-        <v>2.391323288827733</v>
+        <v>-1.784747102288447</v>
       </c>
       <c r="G48">
-        <v>2.682312539965037E-06</v>
+        <v>0.0002589384571907521</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B49" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E49" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="F49">
-        <v>-2.449529678607482</v>
+        <v>2.092330669642934</v>
       </c>
       <c r="G49">
-        <v>3.787880339159282E-05</v>
+        <v>0.0002589384571907521</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D50" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E50" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F50">
-        <v>2.006220421432038</v>
+        <v>2.836022026499688</v>
       </c>
       <c r="G50">
-        <v>0.0001521983888764684</v>
+        <v>3.987116232439306E-18</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F51">
-        <v>-1.91644554320839</v>
+        <v>2.727895477774346</v>
       </c>
       <c r="G51">
-        <v>0.0002160195340481075</v>
+        <v>2.685361711395535E-15</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D52" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E52" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="F52">
-        <v>2.146768268223328</v>
+        <v>2.481725728377683</v>
       </c>
       <c r="G52">
-        <v>0.020334180872511</v>
+        <v>9.119349579616228E-14</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" t="s">
+        <v>97</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" t="s">
+        <v>30</v>
+      </c>
+      <c r="F53">
+        <v>2.525910448327465</v>
+      </c>
+      <c r="G53">
+        <v>5.795644104829686E-13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>97</v>
+      </c>
+      <c r="C54" t="s">
+        <v>54</v>
+      </c>
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" t="s">
+        <v>55</v>
+      </c>
+      <c r="F54">
+        <v>2.534534244421963</v>
+      </c>
+      <c r="G54">
+        <v>2.651466655900934E-09</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55">
+        <v>2.53949220083289</v>
+      </c>
+      <c r="G55">
+        <v>4.713749000153153E-09</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" t="s">
+        <v>97</v>
+      </c>
+      <c r="C56" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56">
+        <v>2.301487125414149</v>
+      </c>
+      <c r="G56">
+        <v>2.468333499875939E-08</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F57">
+        <v>2.36340314333015</v>
+      </c>
+      <c r="G57">
+        <v>9.739869585976538E-07</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" t="s">
         <v>59</v>
       </c>
-      <c r="B53" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="D58" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" t="s">
+        <v>60</v>
+      </c>
+      <c r="F58">
+        <v>-2.229125916720378</v>
+      </c>
+      <c r="G58">
+        <v>0.00237939424016248</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>97</v>
+      </c>
+      <c r="C59" t="s">
+        <v>61</v>
+      </c>
+      <c r="D59" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" t="s">
         <v>62</v>
       </c>
-      <c r="D53" t="s">
+      <c r="F59">
+        <v>-2.230840354268482</v>
+      </c>
+      <c r="G59">
+        <v>0.002442898767015984</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>97</v>
+      </c>
+      <c r="C60" t="s">
+        <v>63</v>
+      </c>
+      <c r="D60" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" t="s">
+        <v>64</v>
+      </c>
+      <c r="F60">
+        <v>-1.829026498962724</v>
+      </c>
+      <c r="G60">
+        <v>0.003221328015687954</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" t="s">
+        <v>97</v>
+      </c>
+      <c r="C61" t="s">
+        <v>65</v>
+      </c>
+      <c r="D61" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" t="s">
+        <v>66</v>
+      </c>
+      <c r="F61">
+        <v>-2.109985236916042</v>
+      </c>
+      <c r="G61">
+        <v>0.005345516941971719</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>58</v>
+      </c>
+      <c r="B62" t="s">
+        <v>97</v>
+      </c>
+      <c r="C62" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" t="s">
         <v>19</v>
       </c>
-      <c r="E53" t="s">
-        <v>63</v>
-      </c>
-      <c r="F53">
-        <v>-2.023043539718842</v>
-      </c>
-      <c r="G53">
-        <v>0.03486707994350972</v>
+      <c r="E62" t="s">
+        <v>68</v>
+      </c>
+      <c r="F62">
+        <v>-2.110326195239017</v>
+      </c>
+      <c r="G62">
+        <v>0.005345516941971719</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>58</v>
+      </c>
+      <c r="B63" t="s">
+        <v>97</v>
+      </c>
+      <c r="C63" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" t="s">
+        <v>70</v>
+      </c>
+      <c r="F63">
+        <v>-1.968855916108449</v>
+      </c>
+      <c r="G63">
+        <v>0.007274026530314413</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>58</v>
+      </c>
+      <c r="B64" t="s">
+        <v>97</v>
+      </c>
+      <c r="C64" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" t="s">
+        <v>72</v>
+      </c>
+      <c r="F64">
+        <v>-2.094233737590684</v>
+      </c>
+      <c r="G64">
+        <v>0.007274026530314413</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>58</v>
+      </c>
+      <c r="B65" t="s">
+        <v>97</v>
+      </c>
+      <c r="C65" t="s">
+        <v>73</v>
+      </c>
+      <c r="D65" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" t="s">
+        <v>74</v>
+      </c>
+      <c r="F65">
+        <v>-1.882139490975687</v>
+      </c>
+      <c r="G65">
+        <v>0.008148644524061697</v>
       </c>
     </row>
   </sheetData>
@@ -2184,117 +2499,117 @@
         <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2309,24 +2624,24 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2341,409 +2656,409 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="B16" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="B17" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="B20" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="B21" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="C23" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="B24" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B25" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C26" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C31" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B32" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B33" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/03_Pathway_Enrichment/05_Volcano/c_data/05_volcano.xlsx
+++ b/03_Pathway_Enrichment/05_Volcano/c_data/05_volcano.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="231">
   <si>
     <t>sheet</t>
   </si>
@@ -374,6 +374,15 @@
     <t>source</t>
   </si>
   <si>
+    <t>BiocGenerics</t>
+  </si>
+  <si>
+    <t>0.58.0</t>
+  </si>
+  <si>
+    <t>Bioconductor 3.23 (R 4.6.0)</t>
+  </si>
+  <si>
     <t>BiocManager</t>
   </si>
   <si>
@@ -383,12 +392,66 @@
     <t>CRAN (R 4.6.0)</t>
   </si>
   <si>
+    <t>circlize</t>
+  </si>
+  <si>
+    <t>0.4.18</t>
+  </si>
+  <si>
     <t>cli</t>
   </si>
   <si>
     <t>3.6.6</t>
   </si>
   <si>
+    <t>clue</t>
+  </si>
+  <si>
+    <t>0.3-68</t>
+  </si>
+  <si>
+    <t>cluster</t>
+  </si>
+  <si>
+    <t>2.1.8.2</t>
+  </si>
+  <si>
+    <t>codetools</t>
+  </si>
+  <si>
+    <t>0.2-20</t>
+  </si>
+  <si>
+    <t>colorspace</t>
+  </si>
+  <si>
+    <t>2.1-2</t>
+  </si>
+  <si>
+    <t>ComplexHeatmap</t>
+  </si>
+  <si>
+    <t>2.28.0</t>
+  </si>
+  <si>
+    <t>crayon</t>
+  </si>
+  <si>
+    <t>1.5.3</t>
+  </si>
+  <si>
+    <t>digest</t>
+  </si>
+  <si>
+    <t>0.6.39</t>
+  </si>
+  <si>
+    <t>doParallel</t>
+  </si>
+  <si>
+    <t>1.0.17</t>
+  </si>
+  <si>
     <t>dplyr</t>
   </si>
   <si>
@@ -401,7 +464,7 @@
     <t>0.3.0.9000</t>
   </si>
   <si>
-    <t>local</t>
+    <t>Github (Dustyn-T-Lewis/enrichVolcano@d3fed631f4ae95e01bd61137699313f8de5cc86e)</t>
   </si>
   <si>
     <t>farver</t>
@@ -410,12 +473,24 @@
     <t>2.1.2</t>
   </si>
   <si>
+    <t>foreach</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
     <t>generics</t>
   </si>
   <si>
     <t>0.1.4</t>
   </si>
   <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
     <t>ggforce</t>
   </si>
   <si>
@@ -434,6 +509,9 @@
     <t>0.9.8</t>
   </si>
   <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
     <t>glue</t>
   </si>
   <si>
@@ -452,6 +530,18 @@
     <t>1.0.2</t>
   </si>
   <si>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
+  </si>
+  <si>
+    <t>iterators</t>
+  </si>
+  <si>
+    <t>1.0.14</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -476,6 +566,12 @@
     <t>7.3-65</t>
   </si>
   <si>
+    <t>matrixStats</t>
+  </si>
+  <si>
+    <t>1.5.0</t>
+  </si>
+  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -488,6 +584,12 @@
     <t>2.0.3</t>
   </si>
   <si>
+    <t>png</t>
+  </si>
+  <si>
+    <t>0.1-9</t>
+  </si>
+  <si>
     <t>polyclip</t>
   </si>
   <si>
@@ -524,6 +626,12 @@
     <t>1.2.3</t>
   </si>
   <si>
+    <t>rjson</t>
+  </si>
+  <si>
+    <t>0.2.23</t>
+  </si>
+  <si>
     <t>rlang</t>
   </si>
   <si>
@@ -539,6 +647,12 @@
     <t>2.1.1</t>
   </si>
   <si>
+    <t>S4Vectors</t>
+  </si>
+  <si>
+    <t>0.50.0</t>
+  </si>
+  <si>
     <t>S7</t>
   </si>
   <si>
@@ -555,6 +669,12 @@
   </si>
   <si>
     <t>1.2.4</t>
+  </si>
+  <si>
+    <t>shape</t>
+  </si>
+  <si>
+    <t>1.4.6.1</t>
   </si>
   <si>
     <t>stringi</t>
@@ -2651,7 +2771,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2684,29 +2804,29 @@
         <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2717,7 +2837,7 @@
         <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2728,7 +2848,7 @@
         <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2739,7 +2859,7 @@
         <v>133</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2750,7 +2870,7 @@
         <v>135</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2772,7 +2892,7 @@
         <v>139</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2783,7 +2903,7 @@
         <v>141</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2794,7 +2914,7 @@
         <v>143</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2805,7 +2925,7 @@
         <v>145</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2816,95 +2936,95 @@
         <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B23" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2915,7 +3035,7 @@
         <v>165</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2926,7 +3046,7 @@
         <v>167</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -2937,15 +3057,15 @@
         <v>169</v>
       </c>
       <c r="C26" t="s">
-        <v>170</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" t="s">
         <v>171</v>
-      </c>
-      <c r="B27" t="s">
-        <v>172</v>
       </c>
       <c r="C27" t="s">
         <v>120</v>
@@ -2953,79 +3073,79 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" t="s">
         <v>173</v>
       </c>
-      <c r="B28" t="s">
-        <v>174</v>
-      </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" t="s">
         <v>175</v>
       </c>
-      <c r="B29" t="s">
-        <v>176</v>
-      </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" t="s">
         <v>177</v>
       </c>
-      <c r="B30" t="s">
-        <v>178</v>
-      </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" t="s">
         <v>179</v>
       </c>
-      <c r="B31" t="s">
-        <v>180</v>
-      </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
+        <v>180</v>
+      </c>
+      <c r="B32" t="s">
         <v>181</v>
       </c>
-      <c r="B32" t="s">
-        <v>182</v>
-      </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B33" t="s">
         <v>183</v>
       </c>
-      <c r="B33" t="s">
-        <v>184</v>
-      </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" t="s">
         <v>185</v>
       </c>
-      <c r="B34" t="s">
-        <v>124</v>
-      </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -3033,32 +3153,252 @@
         <v>186</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>194</v>
+      </c>
+      <c r="B39" t="s">
+        <v>195</v>
+      </c>
+      <c r="C39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>196</v>
+      </c>
+      <c r="B40" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" t="s">
+        <v>199</v>
+      </c>
+      <c r="C41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>200</v>
+      </c>
+      <c r="B42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C42" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>202</v>
+      </c>
+      <c r="B43" t="s">
+        <v>203</v>
+      </c>
+      <c r="C43" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>204</v>
+      </c>
+      <c r="B44" t="s">
+        <v>205</v>
+      </c>
+      <c r="C44" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" t="s">
+        <v>208</v>
+      </c>
+      <c r="C45" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>209</v>
+      </c>
+      <c r="B46" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" t="s">
         <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>211</v>
+      </c>
+      <c r="B47" t="s">
+        <v>212</v>
+      </c>
+      <c r="C47" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" t="s">
+        <v>214</v>
+      </c>
+      <c r="C48" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>215</v>
+      </c>
+      <c r="B49" t="s">
+        <v>216</v>
+      </c>
+      <c r="C49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>217</v>
+      </c>
+      <c r="B50" t="s">
+        <v>218</v>
+      </c>
+      <c r="C50" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>219</v>
+      </c>
+      <c r="B51" t="s">
+        <v>220</v>
+      </c>
+      <c r="C51" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" t="s">
+        <v>221</v>
+      </c>
+      <c r="B52" t="s">
+        <v>222</v>
+      </c>
+      <c r="C52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>223</v>
+      </c>
+      <c r="B53" t="s">
+        <v>224</v>
+      </c>
+      <c r="C53" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" t="s">
+        <v>145</v>
+      </c>
+      <c r="C54" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>226</v>
+      </c>
+      <c r="B55" t="s">
+        <v>187</v>
+      </c>
+      <c r="C55" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" t="s">
+        <v>227</v>
+      </c>
+      <c r="B56" t="s">
+        <v>228</v>
+      </c>
+      <c r="C56" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>229</v>
+      </c>
+      <c r="B57" t="s">
+        <v>230</v>
+      </c>
+      <c r="C57" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
